--- a/backend/database/data.xlsx
+++ b/backend/database/data.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oo1_2.9_1_3" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Лист1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="oo1_2.9_1_3" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Лист1" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'oo1_2.9_1_3'!$A$1:$H$611</definedName>
@@ -1082,7 +1082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:V611"/>
+  <dimension ref="A1:V611"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5.37890625" customWidth="1" style="19" min="1" max="1"/>
@@ -1107,6 +1107,8 @@
     <col width="18.4296875" customWidth="1" style="19" min="22" max="22"/>
   </cols>
   <sheetData>
+    <row r="1"/>
+    <row r="2"/>
     <row r="3" ht="54.75" customHeight="1" s="19">
       <c r="B3" s="12" t="inlineStr">
         <is>
@@ -1260,7 +1262,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Ахматовский р-н</t>
+          <t>Грозный (город)</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1452,7 +1454,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Висаитовский р-н</t>
+          <t>Грозный (город)</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1548,7 +1550,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Ахматовский р-н</t>
+          <t>Грозный (город)</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1644,7 +1646,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Ахматовский р-н</t>
+          <t>Грозный (город)</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1740,7 +1742,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Шейх-Мансуровский р-н</t>
+          <t>Грозный (город)</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -2028,7 +2030,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Ахматовский р-н</t>
+          <t>Грозный (город)</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -2220,7 +2222,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Ахматовский р-н</t>
+          <t>Грозный (город)</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -2412,7 +2414,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Ахматовский р-н</t>
+          <t>Грозный (город)</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2752,7 +2754,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Шейх-Мансуровский р-н</t>
+          <t>Грозный (город)</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2846,7 +2848,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Ахматовский р-н</t>
+          <t>Грозный (город)</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -3128,7 +3130,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Висаитовский р-н</t>
+          <t>Грозный (город)</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -3316,7 +3318,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Шейх-Мансуровский р-н</t>
+          <t>Грозный (город)</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3786,7 +3788,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Ахматовский р-н</t>
+          <t>Грозный (город)</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3974,7 +3976,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Ахматовский р-н</t>
+          <t>Грозный (город)</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -4256,7 +4258,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Ахматовский р-н</t>
+          <t>Грозный (город)</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4444,7 +4446,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Ахматовский р-н</t>
+          <t>Грозный (город)</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4538,7 +4540,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Ахматовский р-н</t>
+          <t>Грозный (город)</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4632,7 +4634,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Шейх-Мансуровский р-н</t>
+          <t>Грозный (город)</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4914,7 +4916,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Байсангуровский р-н</t>
+          <t>Грозный (город)</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -5008,7 +5010,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Ахматовский р-н</t>
+          <t>Грозный (город)</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -5290,7 +5292,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Ахматовский р-н</t>
+          <t>Грозный (город)</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -5384,7 +5386,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Байсангуровский р-н</t>
+          <t>Грозный (город)</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -5478,7 +5480,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Байсангуровский р-н</t>
+          <t>Грозный (город)</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -5572,7 +5574,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Шейх-Мансуровский р-н</t>
+          <t>Грозный (город)</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5666,7 +5668,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Висаитовский р-н</t>
+          <t>Грозный (город)</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5854,7 +5856,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Ахматовский р-н</t>
+          <t>Грозный (город)</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -5948,7 +5950,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Ахматовский р-н</t>
+          <t>Грозный (город)</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -6230,7 +6232,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Шейх-Мансуровский р-н</t>
+          <t>Грозный (город)</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -6418,7 +6420,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Висаитовский р-н</t>
+          <t>Грозный (город)</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -6512,7 +6514,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Ахматовский р-н</t>
+          <t>Грозный (город)</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -6606,7 +6608,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Ахматовский р-н</t>
+          <t>Грозный (город)</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -6700,7 +6702,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Ахматовский р-н</t>
+          <t>Грозный (город)</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -6794,7 +6796,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Шейх-Мансуровский р-н</t>
+          <t>Грозный (город)</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -6888,7 +6890,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Шейх-Мансуровский р-н</t>
+          <t>Грозный (город)</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -6982,7 +6984,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Висаитовский р-н</t>
+          <t>Грозный (город)</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -7076,7 +7078,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Шейх-Мансуровский р-н</t>
+          <t>Грозный (город)</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
